--- a/output/laminas_comunales/comunal_o_ocup_a_2021_maule.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,172 +384,172 @@
         </is>
       </c>
       <c r="C2">
-        <v>40.5314429156748</v>
+        <v>58.5923048464669</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="C3">
-        <v>37.755582366759</v>
+        <v>58.004967163383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C4">
-        <v>37.7238220975328</v>
+        <v>55.2886556318127</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C5">
-        <v>37.5679720121483</v>
+        <v>55.0861326442722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C6">
-        <v>37.5427486497323</v>
+        <v>54.9357744599216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C7">
-        <v>37.5361447054602</v>
+        <v>54.255174291939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C8">
-        <v>37.3983154403422</v>
+        <v>54.1794355760875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="C9">
-        <v>36.1101699700717</v>
+        <v>53.7523556146769</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C10">
-        <v>35.6913036627941</v>
+        <v>53.6511653079478</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C11">
-        <v>35.1245698336426</v>
+        <v>52.9250328391818</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C12">
-        <v>34.2537695798565</v>
+        <v>52.6952167891765</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C13">
-        <v>33.7109449875407</v>
+        <v>52.3265500416518</v>
       </c>
     </row>
     <row r="14">
@@ -564,112 +564,112 @@
         </is>
       </c>
       <c r="C14">
-        <v>33.2796537239164</v>
+        <v>51.7331839362572</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C15">
-        <v>32.6450892857143</v>
+        <v>51.709498046288</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="C16">
-        <v>32.3005467429229</v>
+        <v>51.4259169494264</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C17">
-        <v>32.1182284175978</v>
+        <v>49.7350554727604</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="C18">
-        <v>31.8039285291681</v>
+        <v>49.5696926152693</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="C19">
-        <v>31.771524807002</v>
+        <v>48.8126765536723</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="C20">
-        <v>30.9611290433349</v>
+        <v>48.7430272878034</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="C21">
-        <v>30.7031933508311</v>
+        <v>48.5815602836879</v>
       </c>
     </row>
     <row r="22">
@@ -684,142 +684,2947 @@
         </is>
       </c>
       <c r="C22">
-        <v>30.1030876584052</v>
+        <v>48.5163632173312</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C23">
-        <v>29.5217891917599</v>
+        <v>48.3551779036617</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="C24">
-        <v>29.4502470799641</v>
+        <v>47.9080459770115</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="C25">
-        <v>29.2240343516713</v>
+        <v>47.5855967172353</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="C26">
-        <v>27.921064578368</v>
+        <v>47.510696227149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C27">
-        <v>27.7750212328461</v>
+        <v>47.4118153140235</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="C28">
-        <v>26.6190476190476</v>
+        <v>47.1844428537342</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C29">
-        <v>25.1306888068881</v>
+        <v>46.8607493342089</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C30">
-        <v>24.4648318042813</v>
+        <v>46.8411097099622</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>46.7155412070666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>45.814495188636</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>45.8043456342004</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>45.6553528823212</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>45.2091439688716</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>45.1443142361111</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>45.1256335597973</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>44.8965996403466</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>44.6192112232482</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>44.4669399042023</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>44.4669277632724</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>44.397543340728</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>44.0862384333979</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>43.7296906298687</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>43.4902554894699</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>43.4542622875727</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>43.3080251597474</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>42.9721606555175</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>42.3487360132615</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>41.9500660685722</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>41.8478260869565</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>41.4817383263985</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>41.4396737457679</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>41.3691132172507</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>41.2167449577482</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>40.73679503367</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>40.6876615664082</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>40.5314429156748</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>40.179806362379</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>40.1235684147077</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>39.9856938483548</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>39.5137769590913</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>39.4818776288118</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>39.2904953145917</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>39.2569527811124</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>39.1241965105601</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>39.0129522108084</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>38.8623344074472</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>38.7756078881869</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>38.6854741896759</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>38.2837726214613</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>38.0239953743857</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>37.786860081357</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>37.755582366759</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>37.7344145970603</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>37.7293525509037</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>37.7238220975328</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>37.7221597300337</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>37.6981083844581</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>37.5679720121483</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>37.5427486497323</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>37.5361447054602</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>37.3983154403422</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>37.3173031588873</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>36.796362766212</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>36.2859120803046</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>36.2725133496244</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>36.1101699700717</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>35.9956021518043</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>35.6913036627941</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>35.6663970191695</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>35.6520454881111</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>35.4536134437332</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>35.2428099952852</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>35.1405222738999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>35.1245698336426</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>34.9852507374631</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>34.9385883084577</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>34.9024822695036</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>34.837911682174</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>34.7773239984442</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>34.5229885057471</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>34.2537695798565</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>33.7109449875407</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>33.6004932182491</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>33.5875090777052</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>7203</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Pelluhue</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C107">
+        <v>33.4182761087268</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>33.4139784946237</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>33.3994992846924</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>33.2796537239164</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>33.2347140039448</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>33.0067673906201</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>32.9857033480704</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>32.8444907959211</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>32.8162881599129</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>32.6450892857143</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>32.5813075813076</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>32.5690646473145</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>32.3923868878502</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>32.3593945907218</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>32.3005467429229</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>32.2746286265887</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>32.2408182240818</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>32.1182284175978</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>31.9580099562977</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>31.9373901932599</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>31.8968423418362</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>31.8372343957503</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>31.8039285291681</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>31.771524807002</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>31.6259731068648</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>31.580547112462</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>31.5303867403315</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>31.4699335493797</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>31.2682322053676</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>31.1865312667023</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>31.1634105854562</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>31.060153256705</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>30.9611290433349</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>30.8758705809751</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>30.7031933508311</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>30.5221858705654</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>30.2860615531536</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>30.1030876584052</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>30.0098473658296</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>29.9655520080659</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>29.5217891917599</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>29.4502470799641</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>29.2473606530546</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>29.2240343516713</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>28.8474078904467</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>27.921064578368</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>27.9201133578431</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>27.7750212328461</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>27.7035132819195</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>27.3009506833036</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>26.959675899755</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>26.7814766536315</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>26.643823344979</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>26.6190476190476</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>26.2239856265908</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>25.9812174954166</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>25.7049053688683</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>25.5959266659656</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>25.1306888068881</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>24.820788530466</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>24.6344300432037</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>24.5358282564549</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>24.4648318042813</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>24.1845336265347</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>24.0104514120525</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>23.7435371046229</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>23.421465485419</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>23.1122788176332</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>23.0465575293161</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>22.7954242558863</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>22.7593883081688</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>22.4474474474474</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>22.4083076436645</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>21.8469877006462</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>21.3589743589744</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>20.887753170547</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>20.3566685638399</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C184">
         <v>20.0106590465823</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>19.6936114732725</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>19.424743892829</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>18.3911483253589</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>11.6392443631932</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>11.6128870124648</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>11.4439076757917</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>11.3787317950669</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>11.2163509471585</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>10.8083727447889</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>10.4152302152762</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>10.2728325372702</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>10.2187873357228</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>10.1248502545672</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>9.78695793230237</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>9.663785281054491</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>9.655211171559349</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>9.62891185759403</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>9.38444924406048</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>9.0768115942029</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>8.868717431501089</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>8.68794326241135</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>8.576360497864989</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>8.576229089049599</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>8.410560344827591</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>8.30227743271222</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>8.255741775294849</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>8.215890522875821</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>8.062337486914529</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>8.00049769814607</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>7.9466725214676</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>7.76695363238182</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>6.77275806848978</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>6.35219097449313</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>4.91759088108441</v>
       </c>
     </row>
   </sheetData>
